--- a/MAPA-ORG-002_Papeis-e-Responsabilidades_TIMEWARE.xlsx
+++ b/MAPA-ORG-002_Papeis-e-Responsabilidades_TIMEWARE.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -151,8 +151,58 @@
       <color rgb="00808080"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002E5496"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00843C0C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00BFBFBF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -239,6 +289,16 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -281,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -365,6 +425,45 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -730,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E20"/>
+  <dimension ref="B2:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -781,7 +880,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -939,6 +1038,28 @@
       <c r="E20" s="22" t="inlineStr">
         <is>
           <t>Ajuste de papéis (remoção de COO e DevOps; inclusão de PO e Analista de Requisitos/Sistemas; renomeações de Coordenador SEPG, Auditor de Qualidade, GP e GCO) e sincronização da Matriz RACI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>Time de Melhoria Contínua</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>Reestruturação da aba Matriz RACI no formato 'matriz de conhecimento' (atividades numeradas nas linhas × 14 papéis nas colunas), mantendo a notação R/A/C/I.</t>
         </is>
       </c>
     </row>
@@ -1531,1226 +1652,1670 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="13.5" customWidth="1" min="3" max="3"/>
-    <col width="13.5" customWidth="1" min="4" max="4"/>
-    <col width="13.5" customWidth="1" min="5" max="5"/>
-    <col width="13.5" customWidth="1" min="6" max="6"/>
-    <col width="13.5" customWidth="1" min="7" max="7"/>
-    <col width="13.5" customWidth="1" min="8" max="8"/>
-    <col width="13.5" customWidth="1" min="9" max="9"/>
-    <col width="13.5" customWidth="1" min="10" max="10"/>
-    <col width="13.5" customWidth="1" min="11" max="11"/>
-    <col width="13.5" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="5.4" customWidth="1" min="4" max="4"/>
+    <col width="5.4" customWidth="1" min="5" max="5"/>
+    <col width="5.4" customWidth="1" min="6" max="6"/>
+    <col width="5.4" customWidth="1" min="7" max="7"/>
+    <col width="5.4" customWidth="1" min="8" max="8"/>
+    <col width="5.4" customWidth="1" min="9" max="9"/>
+    <col width="5.4" customWidth="1" min="10" max="10"/>
+    <col width="5.4" customWidth="1" min="11" max="11"/>
+    <col width="5.4" customWidth="1" min="12" max="12"/>
+    <col width="5.4" customWidth="1" min="13" max="13"/>
+    <col width="5.4" customWidth="1" min="14" max="14"/>
+    <col width="5.4" customWidth="1" min="15" max="15"/>
+    <col width="5.4" customWidth="1" min="16" max="16"/>
+    <col width="5.4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>TIMEWARE — Mapa de Papéis e Responsabilidades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>MATRIZ RACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Atividade-chave</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="C1" s="23" t="inlineStr">
-        <is>
-          <t>TMC / SEPG</t>
-        </is>
-      </c>
-      <c r="D1" s="23" t="inlineStr">
-        <is>
-          <t>Resp. Medição</t>
-        </is>
-      </c>
-      <c r="E1" s="23" t="inlineStr">
-        <is>
-          <t>RH / CAP</t>
-        </is>
-      </c>
-      <c r="F1" s="23" t="inlineStr">
-        <is>
-          <t>Auditor Qualidade (GQA)</t>
-        </is>
-      </c>
-      <c r="G1" s="23" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Processo MPS</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>PAPÉIS  —  R = Responsável · A = Autoridade · C = Consultado · I = Informado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="D6" s="36" t="inlineStr">
+        <is>
+          <t>Founder e CEO</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>Time de Melhoria Contínua (SEPG)</t>
+        </is>
+      </c>
+      <c r="F6" s="36" t="inlineStr">
+        <is>
+          <t>Coordenador SEPG</t>
+        </is>
+      </c>
+      <c r="G6" s="36" t="inlineStr">
+        <is>
+          <t>Responsável de Medição</t>
+        </is>
+      </c>
+      <c r="H6" s="36" t="inlineStr">
+        <is>
+          <t>RH / Pessoas / Capacitação</t>
+        </is>
+      </c>
+      <c r="I6" s="36" t="inlineStr">
+        <is>
+          <t>Auditor de  Qualidade (GQA)</t>
+        </is>
+      </c>
+      <c r="J6" s="36" t="inlineStr">
         <is>
           <t>Gerente de Projeto</t>
         </is>
       </c>
-      <c r="H1" s="23" t="inlineStr">
+      <c r="K6" s="36" t="inlineStr">
+        <is>
+          <t>Tech Lead / Arquiteto</t>
+        </is>
+      </c>
+      <c r="L6" s="36" t="inlineStr">
+        <is>
+          <t>Desenvolvedor (DEV)</t>
+        </is>
+      </c>
+      <c r="M6" s="36" t="inlineStr">
+        <is>
+          <t>QA / Testes</t>
+        </is>
+      </c>
+      <c r="N6" s="36" t="inlineStr">
+        <is>
+          <t>Gerente ou analista de Configuração (GCO)</t>
+        </is>
+      </c>
+      <c r="O6" s="36" t="inlineStr">
+        <is>
+          <t>Comercial / Executivo de Contas</t>
+        </is>
+      </c>
+      <c r="P6" s="36" t="inlineStr">
         <is>
           <t>PO</t>
         </is>
       </c>
-      <c r="I1" s="23" t="inlineStr">
-        <is>
-          <t>Analista de Requisitos</t>
-        </is>
-      </c>
-      <c r="J1" s="23" t="inlineStr">
-        <is>
-          <t>Tech Lead / Arquiteto</t>
-        </is>
-      </c>
-      <c r="K1" s="23" t="inlineStr">
-        <is>
-          <t>Equipes (Dev / QA)</t>
-        </is>
-      </c>
-      <c r="L1" s="23" t="inlineStr">
+      <c r="Q6" s="36" t="inlineStr">
+        <is>
+          <t>Analista de Requistos /Analista de sistemas</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>Definir e manter os processos-padrão</t>
+        </is>
+      </c>
+      <c r="C7" s="39" t="inlineStr">
+        <is>
+          <t>GPC</t>
+        </is>
+      </c>
+      <c r="D7" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E7" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F7" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G7" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I7" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J7" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K7" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L7" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M7" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N7" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O7" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="P7" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q7" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>Garantir recursos e orçamento para os processos</t>
+        </is>
+      </c>
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t>OSW</t>
+        </is>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G8" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I8" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K8" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O8" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P8" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q8" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>Conduzir a análise crítica dos processos</t>
+        </is>
+      </c>
+      <c r="C9" s="39" t="inlineStr">
+        <is>
+          <t>OSW</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F9" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G9" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I9" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J9" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K9" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="O9" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="P9" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q9" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>Gerenciar o portfólio e alocar recursos</t>
+        </is>
+      </c>
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t>OSW</t>
+        </is>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="E10" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F10" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H10" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I10" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K10" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L10" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O10" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P10" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q10" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="37" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Planejar e conduzir a capacitação</t>
+        </is>
+      </c>
+      <c r="C11" s="39" t="inlineStr">
+        <is>
+          <t>CAP</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F11" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G11" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I11" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J11" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K11" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L11" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M11" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N11" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="O11" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="P11" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q11" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="38" t="inlineStr">
+        <is>
+          <t>Coletar, analisar e comunicar medições</t>
+        </is>
+      </c>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H12" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I12" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J12" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K12" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L12" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M12" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N12" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="O12" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="P12" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q12" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="38" t="inlineStr">
+        <is>
+          <t>Verificar a aderência ao processo</t>
+        </is>
+      </c>
+      <c r="C13" s="39" t="inlineStr">
+        <is>
+          <t>GQA</t>
+        </is>
+      </c>
+      <c r="D13" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F13" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G13" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H13" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I13" s="44" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="J13" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K13" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L13" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M13" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N13" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O13" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P13" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q13" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>Priorizar e implementar melhorias</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>GPC</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F14" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G14" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H14" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I14" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J14" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K14" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L14" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M14" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N14" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O14" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="P14" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q14" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="37" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>Abrir e planejar o projeto (TAP / Plano)</t>
+        </is>
+      </c>
+      <c r="C15" s="39" t="inlineStr">
+        <is>
+          <t>GPR</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G15" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H15" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I15" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J15" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K15" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L15" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M15" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N15" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O15" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P15" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q15" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>Levantar e validar requisitos</t>
+        </is>
+      </c>
+      <c r="C16" s="39" t="inlineStr">
+        <is>
+          <t>REQ</t>
+        </is>
+      </c>
+      <c r="D16" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H16" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J16" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K16" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L16" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M16" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N16" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="O16" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P16" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q16" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="37" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="38" t="inlineStr">
+        <is>
+          <t>Projetar e construir o produto</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="inlineStr">
+        <is>
+          <t>PCP</t>
+        </is>
+      </c>
+      <c r="D17" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H17" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J17" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K17" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L17" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="M17" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N17" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O17" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P17" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q17" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="38" t="inlineStr">
+        <is>
+          <t>Integrar o produto</t>
+        </is>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>ITP</t>
+        </is>
+      </c>
+      <c r="D18" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H18" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J18" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K18" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L18" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="M18" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N18" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O18" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P18" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q18" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="37" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="38" t="inlineStr">
+        <is>
+          <t>Verificar e validar / revisão por pares</t>
+        </is>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>VV</t>
+        </is>
+      </c>
+      <c r="D19" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H19" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J19" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K19" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L19" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="M19" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N19" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O19" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P19" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q19" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="37" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="38" t="inlineStr">
+        <is>
+          <t>Gerenciar configuração e baselines</t>
+        </is>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
         <is>
           <t>GCO</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Definir e manter os processos-padrão</t>
-        </is>
-      </c>
-      <c r="B2" s="25" t="inlineStr">
+      <c r="D20" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F20" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H20" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J20" s="42" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="K20" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L20" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M20" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E2" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F2" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G2" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H2" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I2" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J2" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K2" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L2" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
-        <is>
-          <t>Garantir recursos e orçamento para os processos</t>
-        </is>
-      </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="O20" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P20" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Q20" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="38" t="inlineStr">
+        <is>
+          <t>Gerenciar mudanças de escopo (Change Request)</t>
+        </is>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>GPR</t>
+        </is>
+      </c>
+      <c r="D21" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E21" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H21" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J21" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K21" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L21" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M21" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N21" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O21" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P21" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q21" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="37" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" s="38" t="inlineStr">
+        <is>
+          <t>Registrar decisões relevantes</t>
+        </is>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>GDE</t>
+        </is>
+      </c>
+      <c r="D22" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E22" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H22" s="45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J22" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K22" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L22" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M22" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N22" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="O22" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="P22" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q22" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="37" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="38" t="inlineStr">
+        <is>
+          <t>Encerrar o projeto e obter o aceite</t>
+        </is>
+      </c>
+      <c r="C23" s="39" t="inlineStr">
+        <is>
+          <t>GPR</t>
+        </is>
+      </c>
+      <c r="D23" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E23" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H23" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I23" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J23" s="41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K23" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L23" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="M23" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N23" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O23" s="43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P23" s="42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Q23" s="40" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>Legenda RACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Responsável pela execução</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Autoridade — aprova/decide</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D3" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F3" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G3" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K3" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L3" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
-        <is>
-          <t>Conduzir a análise crítica dos processos</t>
-        </is>
-      </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D4" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E4" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F4" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G4" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H4" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I4" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K4" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L4" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
-        <is>
-          <t>Gerenciar o portfólio e alocar recursos</t>
-        </is>
-      </c>
-      <c r="B5" s="29" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D5" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E5" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F5" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H5" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I5" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K5" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t>Planejar e conduzir a capacitação</t>
-        </is>
-      </c>
-      <c r="B6" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C6" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D6" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F6" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G6" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H6" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I6" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J6" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K6" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L6" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>Coletar, analisar e comunicar medições</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C7" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E7" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F7" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G7" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H7" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I7" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J7" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K7" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L7" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>Verificar a aderência ao processo (GQA)</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F8" s="29" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="G8" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H8" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I8" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J8" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K8" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L8" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>Priorizar e implementar melhorias</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D9" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F9" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G9" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H9" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I9" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J9" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K9" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L9" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>Abrir e planejar o projeto (TAP / Plano)</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C10" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D10" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E10" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G10" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H10" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I10" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J10" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K10" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L10" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>Levantar e validar requisitos (REQ)</t>
-        </is>
-      </c>
-      <c r="B11" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D11" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E11" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H11" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I11" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J11" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K11" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L11" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>Projetar e construir o produto (PCP)</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C12" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D12" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E12" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G12" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H12" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I12" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J12" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K12" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L12" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>Integrar o produto (ITP)</t>
-        </is>
-      </c>
-      <c r="B13" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E13" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G13" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H13" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I13" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J13" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K13" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L13" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>Verificar e validar / revisão por pares (VV)</t>
-        </is>
-      </c>
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C14" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D14" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E14" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G14" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H14" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I14" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J14" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K14" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L14" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>Gerenciar configuração e baselines (GCO)</t>
-        </is>
-      </c>
-      <c r="B15" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C15" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D15" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E15" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G15" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H15" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="I15" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J15" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K15" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L15" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>Gerenciar mudanças de escopo (Change Request)</t>
-        </is>
-      </c>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C16" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D16" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E16" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G16" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H16" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I16" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J16" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K16" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L16" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>Registrar decisões relevantes (GDE)</t>
-        </is>
-      </c>
-      <c r="B17" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C17" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D17" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E17" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G17" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H17" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I17" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J17" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K17" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L17" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>Encerrar o projeto e obter o aceite (TAE)</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D18" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G18" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H18" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I18" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="J18" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K18" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L18" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="31" t="inlineStr">
-        <is>
-          <t>Legenda RACI</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="26" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Responsável pela execução</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>Autoridade — aprova/decide</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t>R/A</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>Executa e decide</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>Consultado</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="27" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>Informado</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>Não participa</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>Nota: a coluna 'TMC / SEPG' representa o Time de Melhoria Contínua, incluindo o Coordenador SEPG.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="D5:Q5"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>